--- a/data/Zone Distribution Aug 2026 w location type.xlsx
+++ b/data/Zone Distribution Aug 2026 w location type.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AFTAB_ACI\Rasel Sir Monthly Report\Zone Distribution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A4C98A-DE12-462D-A72D-7C9D850A2897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED797B6C-6CFE-4FDA-9621-D364D7032BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C5DBF2E-402A-4C22-98D9-03D7E4F06297}"/>
   </bookViews>
@@ -9762,9 +9762,6 @@
     <t>Mr. Kaushik</t>
   </si>
   <si>
-    <t>Shahariar Sumon</t>
-  </si>
-  <si>
     <t>Mr. Sumon</t>
   </si>
   <si>
@@ -9772,6 +9769,9 @@
   </si>
   <si>
     <t>MD. Afzal Hossain</t>
+  </si>
+  <si>
+    <t>Shahriar Sumon</t>
   </si>
 </sst>
 </file>
@@ -12279,7 +12279,7 @@
         <v>18741</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>2298</v>
@@ -12359,7 +12359,7 @@
         <v>18741</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>2298</v>
@@ -12439,7 +12439,7 @@
         <v>18741</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>2298</v>
@@ -12519,7 +12519,7 @@
         <v>18741</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>2298</v>
@@ -12599,7 +12599,7 @@
         <v>18741</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>2298</v>
@@ -12679,7 +12679,7 @@
         <v>18741</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>2298</v>
@@ -12759,7 +12759,7 @@
         <v>18741</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>2298</v>
@@ -12839,7 +12839,7 @@
         <v>18741</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>2298</v>
@@ -12919,7 +12919,7 @@
         <v>18741</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>2298</v>
@@ -12999,7 +12999,7 @@
         <v>18741</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>2298</v>
@@ -13079,7 +13079,7 @@
         <v>18741</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>2298</v>
@@ -51067,7 +51067,7 @@
         <v>39616</v>
       </c>
       <c r="E506" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F506" s="8" t="s">
         <v>3239</v>
@@ -51147,7 +51147,7 @@
         <v>39616</v>
       </c>
       <c r="E507" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F507" s="8" t="s">
         <v>3239</v>
@@ -51227,7 +51227,7 @@
         <v>39616</v>
       </c>
       <c r="E508" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F508" s="8" t="s">
         <v>3239</v>
@@ -51307,7 +51307,7 @@
         <v>39616</v>
       </c>
       <c r="E509" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F509" s="8" t="s">
         <v>3239</v>
@@ -51387,7 +51387,7 @@
         <v>39616</v>
       </c>
       <c r="E510" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F510" s="8" t="s">
         <v>3239</v>
@@ -51467,7 +51467,7 @@
         <v>39616</v>
       </c>
       <c r="E511" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F511" s="8" t="s">
         <v>3239</v>
@@ -51547,7 +51547,7 @@
         <v>39616</v>
       </c>
       <c r="E512" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F512" s="8" t="s">
         <v>3239</v>
@@ -51627,7 +51627,7 @@
         <v>39616</v>
       </c>
       <c r="E513" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F513" s="8" t="s">
         <v>3239</v>
@@ -51707,7 +51707,7 @@
         <v>39616</v>
       </c>
       <c r="E514" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F514" s="8" t="s">
         <v>3239</v>
@@ -51787,7 +51787,7 @@
         <v>39616</v>
       </c>
       <c r="E515" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F515" s="8" t="s">
         <v>3239</v>
@@ -51867,7 +51867,7 @@
         <v>39616</v>
       </c>
       <c r="E516" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F516" s="8" t="s">
         <v>3239</v>
@@ -51947,7 +51947,7 @@
         <v>39616</v>
       </c>
       <c r="E517" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F517" s="8" t="s">
         <v>3239</v>
@@ -52027,7 +52027,7 @@
         <v>39616</v>
       </c>
       <c r="E518" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F518" s="8" t="s">
         <v>3239</v>
@@ -52107,7 +52107,7 @@
         <v>39616</v>
       </c>
       <c r="E519" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F519" s="8" t="s">
         <v>3239</v>
@@ -52187,7 +52187,7 @@
         <v>39616</v>
       </c>
       <c r="E520" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F520" s="8" t="s">
         <v>3239</v>
@@ -52267,7 +52267,7 @@
         <v>39616</v>
       </c>
       <c r="E521" s="8" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="F521" s="8" t="s">
         <v>3239</v>
@@ -52439,10 +52439,10 @@
         <v>16223</v>
       </c>
       <c r="I523" s="8" t="s">
+        <v>3243</v>
+      </c>
+      <c r="J523" s="8" t="s">
         <v>3240</v>
-      </c>
-      <c r="J523" s="8" t="s">
-        <v>3241</v>
       </c>
       <c r="K523" s="8">
         <v>1847265127</v>
@@ -52519,10 +52519,10 @@
         <v>16223</v>
       </c>
       <c r="I524" s="8" t="s">
+        <v>3243</v>
+      </c>
+      <c r="J524" s="8" t="s">
         <v>3240</v>
-      </c>
-      <c r="J524" s="8" t="s">
-        <v>3241</v>
       </c>
       <c r="K524" s="8">
         <v>1847265127</v>
